--- a/src/test/resources/TEST_DATA/MessagesPageData.xlsx
+++ b/src/test/resources/TEST_DATA/MessagesPageData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="9"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="MDraftMessageData" sheetId="1" state="visible" r:id="rId1"/>
@@ -129,7 +129,7 @@
     <t>Hikkaduwa</t>
   </si>
   <si>
-    <t>kolithal</t>
+    <t>sushenw</t>
   </si>
   <si>
     <t xml:space="preserve">Auto FTD message</t>
@@ -307,7 +307,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1"/>
@@ -320,6 +320,7 @@
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -964,7 +965,7 @@
       <c r="G2" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="7" t="s">
         <v>76</v>
       </c>
       <c r="I2" s="2" t="s">
@@ -985,6 +986,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col bestFit="1" min="8" max="8" width="9.421875"/>
+  </cols>
   <sheetData>
     <row r="1" ht="14.25">
       <c r="A1" t="s">
@@ -1583,7 +1587,7 @@
       <c r="H2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="6" t="s">
         <v>34</v>
       </c>
       <c r="J2" s="2" t="s">

--- a/src/test/resources/TEST_DATA/MessagesPageData.xlsx
+++ b/src/test/resources/TEST_DATA/MessagesPageData.xlsx
@@ -126,7 +126,7 @@
     <t xml:space="preserve">Auto OS message</t>
   </si>
   <si>
-    <t>Hikkaduwa</t>
+    <t>HIKKADUWA</t>
   </si>
   <si>
     <t>sushenw</t>
@@ -317,10 +317,10 @@
     <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1147,6 +1147,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col customWidth="1" min="6" max="6" width="14.421875"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
@@ -1196,7 +1199,7 @@
       <c r="E2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="5" t="s">
         <v>33</v>
       </c>
       <c r="G2" s="2" t="s">
@@ -1566,7 +1569,7 @@
       <c r="A2" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>33</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -1587,7 +1590,7 @@
       <c r="H2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="2" t="s">
         <v>34</v>
       </c>
       <c r="J2" s="2" t="s">
